--- a/data/nzd0098/nzd0098.xlsx
+++ b/data/nzd0098/nzd0098.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E302"/>
+  <dimension ref="A1:E303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6774,6 +6774,27 @@
       <c r="E302" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>406.01</v>
+      </c>
+      <c r="C303" t="n">
+        <v>384.05</v>
+      </c>
+      <c r="D303" t="n">
+        <v>385.47</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B340"/>
+  <dimension ref="A1:B341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10191,6 +10212,16 @@
       </c>
       <c r="B340" t="n">
         <v>-0.37</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>1.14</v>
       </c>
     </row>
   </sheetData>
@@ -10359,28 +10390,28 @@
         <v>0.1078</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.002245477076494609</v>
+        <v>-0.0009971289465651012</v>
       </c>
       <c r="J2" t="n">
+        <v>302</v>
+      </c>
+      <c r="K2" t="n">
         <v>301</v>
       </c>
-      <c r="K2" t="n">
-        <v>300</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.937031356047392e-05</v>
+        <v>3.842767672956882e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>2.996771891215761</v>
+        <v>2.993069902285241</v>
       </c>
       <c r="N2" t="n">
-        <v>13.57644676727764</v>
+        <v>13.5431350888818</v>
       </c>
       <c r="O2" t="n">
-        <v>3.684623015625565</v>
+        <v>3.680099874851469</v>
       </c>
       <c r="P2" t="n">
-        <v>404.1728190726793</v>
+        <v>404.1592651385159</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10437,28 +10468,28 @@
         <v>0.1081</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1033223447698653</v>
+        <v>-0.1067910673042199</v>
       </c>
       <c r="J3" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K3" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06004377451293053</v>
+        <v>0.06366426031663874</v>
       </c>
       <c r="M3" t="n">
-        <v>2.215509580284239</v>
+        <v>2.226639106002612</v>
       </c>
       <c r="N3" t="n">
-        <v>8.826781282274219</v>
+        <v>8.890290194127356</v>
       </c>
       <c r="O3" t="n">
-        <v>2.970989949877687</v>
+        <v>2.981658966771243</v>
       </c>
       <c r="P3" t="n">
-        <v>392.0880861491395</v>
+        <v>392.1254337922496</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10515,28 +10546,28 @@
         <v>0.0669</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3073989984415808</v>
+        <v>-0.3065581272177405</v>
       </c>
       <c r="J4" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K4" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3116060701686922</v>
+        <v>0.311794714314611</v>
       </c>
       <c r="M4" t="n">
-        <v>2.44566158740015</v>
+        <v>2.441414476519859</v>
       </c>
       <c r="N4" t="n">
-        <v>11.02580315096539</v>
+        <v>10.99474355310946</v>
       </c>
       <c r="O4" t="n">
-        <v>3.320512483181683</v>
+        <v>3.315832256479428</v>
       </c>
       <c r="P4" t="n">
-        <v>392.263801470558</v>
+        <v>392.2547478324943</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -10574,7 +10605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E302"/>
+  <dimension ref="A1:E303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18727,6 +18758,33 @@
         </is>
       </c>
     </row>
+    <row r="303">
+      <c r="A303" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>-35.71447727453893,174.53774307438005</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>-35.71460202528876,174.53863848971778</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>-35.71437067142919,174.53944472620887</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0098/nzd0098.xlsx
+++ b/data/nzd0098/nzd0098.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E303"/>
+  <dimension ref="A1:E305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6793,6 +6793,48 @@
         <v>385.47</v>
       </c>
       <c r="E303" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>406.01</v>
+      </c>
+      <c r="C304" t="n">
+        <v>381.93</v>
+      </c>
+      <c r="D304" t="n">
+        <v>383.17</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>406.75</v>
+      </c>
+      <c r="C305" t="n">
+        <v>383.02</v>
+      </c>
+      <c r="D305" t="n">
+        <v>383.26</v>
+      </c>
+      <c r="E305" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -6809,7 +6851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B341"/>
+  <dimension ref="A1:B343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10222,6 +10264,26 @@
       </c>
       <c r="B341" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -10390,28 +10452,28 @@
         <v>0.1078</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0009971289465651012</v>
+        <v>0.001925349049517393</v>
       </c>
       <c r="J2" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K2" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L2" t="n">
-        <v>3.842767672956882e-06</v>
+        <v>1.448870603681929e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.993069902285241</v>
+        <v>2.987755428240711</v>
       </c>
       <c r="N2" t="n">
-        <v>13.5431350888818</v>
+        <v>13.48725249296282</v>
       </c>
       <c r="O2" t="n">
-        <v>3.680099874851469</v>
+        <v>3.672499488490477</v>
       </c>
       <c r="P2" t="n">
-        <v>404.1592651385159</v>
+        <v>404.1274238542242</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10468,28 +10530,28 @@
         <v>0.1081</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1067910673042199</v>
+        <v>-0.1155920477574984</v>
       </c>
       <c r="J3" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K3" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06366426031663874</v>
+        <v>0.07242030846709036</v>
       </c>
       <c r="M3" t="n">
-        <v>2.226639106002612</v>
+        <v>2.258823601751004</v>
       </c>
       <c r="N3" t="n">
-        <v>8.890290194127356</v>
+        <v>9.135036951922251</v>
       </c>
       <c r="O3" t="n">
-        <v>2.981658966771243</v>
+        <v>3.022422364912332</v>
       </c>
       <c r="P3" t="n">
-        <v>392.1254337922496</v>
+        <v>392.2205157592996</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10546,28 +10608,28 @@
         <v>0.0669</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3065581272177405</v>
+        <v>-0.3077920454958463</v>
       </c>
       <c r="J4" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K4" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L4" t="n">
-        <v>0.311794714314611</v>
+        <v>0.3163449036777356</v>
       </c>
       <c r="M4" t="n">
-        <v>2.441414476519859</v>
+        <v>2.432137909195826</v>
       </c>
       <c r="N4" t="n">
-        <v>10.99474355310946</v>
+        <v>10.92834832587339</v>
       </c>
       <c r="O4" t="n">
-        <v>3.315832256479428</v>
+        <v>3.305805246210579</v>
       </c>
       <c r="P4" t="n">
-        <v>392.2547478324943</v>
+        <v>392.2680787294278</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -10605,7 +10667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E303"/>
+  <dimension ref="A1:E305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18785,6 +18847,60 @@
         </is>
       </c>
     </row>
+    <row r="304">
+      <c r="A304" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:12:01+00:00</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>-35.71447727453893,174.53774307438005</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>-35.714620664537215,174.53864365950776</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>-35.714390272879534,174.5394530088484</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>-35.71447064809598,174.5377421356033</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>-35.714611081150075,174.53864100145506</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>-35.714389505866265,174.53945268474502</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0098/nzd0098.xlsx
+++ b/data/nzd0098/nzd0098.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E305"/>
+  <dimension ref="A1:E307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6835,6 +6835,48 @@
         <v>383.26</v>
       </c>
       <c r="E305" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>410.2</v>
+      </c>
+      <c r="C306" t="n">
+        <v>381.64</v>
+      </c>
+      <c r="D306" t="n">
+        <v>382.63</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>405.54</v>
+      </c>
+      <c r="C307" t="n">
+        <v>383.87</v>
+      </c>
+      <c r="D307" t="n">
+        <v>382.34</v>
+      </c>
+      <c r="E307" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -6851,7 +6893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B343"/>
+  <dimension ref="A1:B345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10284,6 +10326,26 @@
       </c>
       <c r="B343" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>-0.63</v>
       </c>
     </row>
   </sheetData>
@@ -10452,28 +10514,28 @@
         <v>0.1078</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001925349049517393</v>
+        <v>0.006739229481838971</v>
       </c>
       <c r="J2" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K2" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L2" t="n">
-        <v>1.448870603681929e-05</v>
+        <v>0.0001783457195005944</v>
       </c>
       <c r="M2" t="n">
-        <v>2.987755428240711</v>
+        <v>2.991295059160781</v>
       </c>
       <c r="N2" t="n">
-        <v>13.48725249296282</v>
+        <v>13.52206856174227</v>
       </c>
       <c r="O2" t="n">
-        <v>3.672499488490477</v>
+        <v>3.677236538726095</v>
       </c>
       <c r="P2" t="n">
-        <v>404.1274238542242</v>
+        <v>404.0744334262694</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10530,28 +10592,28 @@
         <v>0.1081</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1155920477574984</v>
+        <v>-0.1238403770936253</v>
       </c>
       <c r="J3" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K3" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07242030846709036</v>
+        <v>0.08109397477387992</v>
       </c>
       <c r="M3" t="n">
-        <v>2.258823601751004</v>
+        <v>2.288675548069665</v>
       </c>
       <c r="N3" t="n">
-        <v>9.135036951922251</v>
+        <v>9.344728429562048</v>
       </c>
       <c r="O3" t="n">
-        <v>3.022422364912332</v>
+        <v>3.056914854810655</v>
       </c>
       <c r="P3" t="n">
-        <v>392.2205157592996</v>
+        <v>392.3106079220461</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10608,28 +10670,28 @@
         <v>0.0669</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3077920454958463</v>
+        <v>-0.3098484348157769</v>
       </c>
       <c r="J4" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K4" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3163449036777356</v>
+        <v>0.3219357667056939</v>
       </c>
       <c r="M4" t="n">
-        <v>2.432137909195826</v>
+        <v>2.427231642321106</v>
       </c>
       <c r="N4" t="n">
-        <v>10.92834832587339</v>
+        <v>10.87326224650561</v>
       </c>
       <c r="O4" t="n">
-        <v>3.305805246210579</v>
+        <v>3.297463001537032</v>
       </c>
       <c r="P4" t="n">
-        <v>392.2680787294278</v>
+        <v>392.2905451704444</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -10667,7 +10729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E305"/>
+  <dimension ref="A1:E307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18901,6 +18963,60 @@
         </is>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>-35.714439754544124,174.53773775887643</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>-35.714623214245705,174.53864436669625</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>-35.714394874959076,174.5394549534687</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>-35.71448148322568,174.53774367063016</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>-35.714603607866486,174.53863892866212</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>-35.714397346446226,174.53945599780192</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0098/nzd0098.xlsx
+++ b/data/nzd0098/nzd0098.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E307"/>
+  <dimension ref="A1:E310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6877,6 +6877,69 @@
         <v>382.34</v>
       </c>
       <c r="E307" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>406.19</v>
+      </c>
+      <c r="C308" t="n">
+        <v>385.22</v>
+      </c>
+      <c r="D308" t="n">
+        <v>383.56</v>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>406.67</v>
+      </c>
+      <c r="C309" t="n">
+        <v>384.81</v>
+      </c>
+      <c r="D309" t="n">
+        <v>382.76</v>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>407.32</v>
+      </c>
+      <c r="C310" t="n">
+        <v>385.75</v>
+      </c>
+      <c r="D310" t="n">
+        <v>381.02</v>
+      </c>
+      <c r="E310" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -6893,7 +6956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B345"/>
+  <dimension ref="A1:B348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10346,6 +10409,36 @@
       </c>
       <c r="B345" t="n">
         <v>-0.63</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>-0.12</v>
       </c>
     </row>
   </sheetData>
@@ -10514,28 +10607,28 @@
         <v>0.1078</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006739229481838971</v>
+        <v>0.01147080118227184</v>
       </c>
       <c r="J2" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K2" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001783457195005944</v>
+        <v>0.0005249254033523609</v>
       </c>
       <c r="M2" t="n">
-        <v>2.991295059160781</v>
+        <v>2.984470827234798</v>
       </c>
       <c r="N2" t="n">
-        <v>13.52206856174227</v>
+        <v>13.45010151883356</v>
       </c>
       <c r="O2" t="n">
-        <v>3.677236538726095</v>
+        <v>3.6674380047703</v>
       </c>
       <c r="P2" t="n">
-        <v>404.0744334262694</v>
+        <v>404.0221275964424</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10592,28 +10685,28 @@
         <v>0.1081</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1238403770936253</v>
+        <v>-0.1309343625747318</v>
       </c>
       <c r="J3" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K3" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08109397477387992</v>
+        <v>0.09029736157547119</v>
       </c>
       <c r="M3" t="n">
-        <v>2.288675548069665</v>
+        <v>2.30541602697651</v>
       </c>
       <c r="N3" t="n">
-        <v>9.344728429562048</v>
+        <v>9.387593583411542</v>
       </c>
       <c r="O3" t="n">
-        <v>3.056914854810655</v>
+        <v>3.063918011861861</v>
       </c>
       <c r="P3" t="n">
-        <v>392.3106079220461</v>
+        <v>392.3883700502008</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10670,28 +10763,28 @@
         <v>0.0669</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3098484348157769</v>
+        <v>-0.3128270949743646</v>
       </c>
       <c r="J4" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="K4" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3219357667056939</v>
+        <v>0.3299500721875167</v>
       </c>
       <c r="M4" t="n">
-        <v>2.427231642321106</v>
+        <v>2.419588320858126</v>
       </c>
       <c r="N4" t="n">
-        <v>10.87326224650561</v>
+        <v>10.80165419607429</v>
       </c>
       <c r="O4" t="n">
-        <v>3.297463001537032</v>
+        <v>3.286587013312487</v>
       </c>
       <c r="P4" t="n">
-        <v>392.2905451704444</v>
+        <v>392.3232221381018</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -10729,7 +10822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E307"/>
+  <dimension ref="A1:E310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19017,6 +19110,87 @@
         </is>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>-35.71447566270147,174.53774284602892</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>-35.714591738533585,174.5386356365801</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>-35.71438694915539,174.53945160440054</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>-35.714471364468196,174.53774223709271</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>-35.71459534329396,174.53863663639748</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>-35.71439376705104,174.53945448531934</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>-35.71446554394397,174.53774141249167</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>-35.71458707872137,174.53863434413333</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>-35.71440859597377,174.53946075131955</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0098/nzd0098.xlsx
+++ b/data/nzd0098/nzd0098.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E310"/>
+  <dimension ref="A1:E311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6942,6 +6942,27 @@
       <c r="E310" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>407.57</v>
+      </c>
+      <c r="C311" t="n">
+        <v>386.78</v>
+      </c>
+      <c r="D311" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B348"/>
+  <dimension ref="A1:B349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10439,6 +10460,16 @@
       </c>
       <c r="B348" t="n">
         <v>-0.12</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -10607,28 +10638,28 @@
         <v>0.1078</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01147080118227184</v>
+        <v>0.01353497947738615</v>
       </c>
       <c r="J2" t="n">
+        <v>310</v>
+      </c>
+      <c r="K2" t="n">
         <v>309</v>
       </c>
-      <c r="K2" t="n">
-        <v>308</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0005249254033523609</v>
+        <v>0.0007338466749524652</v>
       </c>
       <c r="M2" t="n">
-        <v>2.984470827234798</v>
+        <v>2.98444766431406</v>
       </c>
       <c r="N2" t="n">
-        <v>13.45010151883356</v>
+        <v>13.44016733603142</v>
       </c>
       <c r="O2" t="n">
-        <v>3.6674380047703</v>
+        <v>3.666083378215971</v>
       </c>
       <c r="P2" t="n">
-        <v>404.0221275964424</v>
+        <v>403.9992201236457</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -10685,28 +10716,28 @@
         <v>0.1081</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1309343625747318</v>
+        <v>-0.1322603031112052</v>
       </c>
       <c r="J3" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K3" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09029736157547119</v>
+        <v>0.09240694926771975</v>
       </c>
       <c r="M3" t="n">
-        <v>2.30541602697651</v>
+        <v>2.305311275022892</v>
       </c>
       <c r="N3" t="n">
-        <v>9.387593583411542</v>
+        <v>9.371425633372937</v>
       </c>
       <c r="O3" t="n">
-        <v>3.063918011861861</v>
+        <v>3.061278431206958</v>
       </c>
       <c r="P3" t="n">
-        <v>392.3883700502008</v>
+        <v>392.4029656155972</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -10763,28 +10794,28 @@
         <v>0.0669</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3128270949743646</v>
+        <v>-0.3140079493072895</v>
       </c>
       <c r="J4" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K4" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3299500721875167</v>
+        <v>0.3328898556885811</v>
       </c>
       <c r="M4" t="n">
-        <v>2.419588320858126</v>
+        <v>2.418066931089225</v>
       </c>
       <c r="N4" t="n">
-        <v>10.80165419607429</v>
+        <v>10.77800487551994</v>
       </c>
       <c r="O4" t="n">
-        <v>3.286587013312487</v>
+        <v>3.282987187839749</v>
       </c>
       <c r="P4" t="n">
-        <v>392.3232221381018</v>
+        <v>392.3362206370281</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -10822,7 +10853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E310"/>
+  <dimension ref="A1:E311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19191,6 +19222,33 @@
         </is>
       </c>
     </row>
+    <row r="311">
+      <c r="A311" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>-35.714463305280795,174.53774109533745</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>-35.71457802285984,174.53863183239767</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>-35.71439964748597,174.53945697011224</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
